--- a/common/excel/xls/equipment.xlsx
+++ b/common/excel/xls/equipment.xlsx
@@ -1727,8 +1727,8 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="84.5723648071289" customWidth="1"/>
@@ -1736,273 +1736,539 @@
     <col min="3" max="3" width="22.40069580078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>4</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>5</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>6</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>7</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>8</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>9</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>10</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>11</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>12</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>13</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>14</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>15</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>16</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>17</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>18</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>19</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>20</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>21</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>22</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>23</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="0">
-        <v>8</v>
+    <row r="1" spans="1:1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>convert(equipment.txt,EquipmentSubCategoryConf.pb,EquipmentSubCategoryConf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t>EquipmentSubCategoryId</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t>EquipmentSubCategoryName</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t>EquipmentCategoryId</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t>EquipmentMaxSlot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="0">
+        <is>
+          <t>爪</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="0">
+        <is>
+          <t>匕首</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="0">
+        <is>
+          <t>魔杖</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t>单手剑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="0">
+        <is>
+          <t>单手斧</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t>单手锤</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t>权杖</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t>弓</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t>双手剑</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t>双手斧</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t>双手锤</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t>长矛</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t>法杖</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="inlineStr" s="0">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="0">
+        <is>
+          <t>头盔</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="inlineStr" s="0">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t>胸甲</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="inlineStr" s="0">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="0">
+        <is>
+          <t>手套</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="0">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="inlineStr" s="0">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="0">
+        <is>
+          <t>鞋子</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="0">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="inlineStr" s="0">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="0">
+        <is>
+          <t>腰带</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="0">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="0">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="0">
+        <is>
+          <t>戒指</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="0">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="inlineStr" s="0">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="0">
+        <is>
+          <t>项链</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="0">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="0">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="inlineStr" s="0">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="0">
+        <is>
+          <t>盾牌</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="0">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="inlineStr" s="0">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="0">
+        <is>
+          <t>箭袋</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="0">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="inlineStr" s="0">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="0">
+        <is>
+          <t>法器</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="0">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="0">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
   </sheetData>
